--- a/data/lookups/dominio.xlsx
+++ b/data/lookups/dominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\TOOLS\KNOWLEDGE SHARING\ProID\data\lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E569114C-C39C-48F8-967F-34ACC988E75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D80D541-9B53-4112-92DD-CB3B2344EC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$A$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$A$36</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>value</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Transizione energetica</t>
+  </si>
+  <si>
+    <t>Commercio</t>
+  </si>
+  <si>
+    <t>Commercio di prossimità</t>
   </si>
 </sst>
 </file>
@@ -413,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A1009"/>
+  <dimension ref="A1:A1011"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.6328125" customWidth="1"/>
@@ -457,146 +463,154 @@
     </row>
     <row r="8" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>25</v>
+      <c r="A26" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
+      <c r="A28" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>34</v>
+      <c r="A30" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>30</v>
+      <c r="A32" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1569,10 +1583,12 @@
     <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:A34" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A35">
-      <sortCondition ref="A1:A34"/>
+  <autoFilter ref="A1:A36" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A37">
+      <sortCondition ref="A1:A36"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
